--- a/dist/templates/MARY_Plantilla_Presupuesto_EN.xlsx
+++ b/dist/templates/MARY_Plantilla_Presupuesto_EN.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Reference" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget EN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-  </numFmts>
-  <fonts count="9">
+  <numFmts count="0"/>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,38 +30,45 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="0094A3B8"/>
+      <color rgb="009CA3AF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="8"/>
+      <i val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00475569"/>
-      <sz val="8"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00166534"/>
-      <sz val="9"/>
+      <color rgb="00065F46"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="009CA3AF"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -72,7 +77,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,56 +86,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E2A4A"/>
+        <fgColor rgb="001B3A6B"/>
+        <bgColor rgb="001B3A6B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D9488"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E8F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF9C3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="001D9E75"/>
+        <bgColor rgb="001D9E75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2FF"/>
+        <bgColor rgb="00EEF2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -139,78 +136,90 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="medium"/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -577,316 +586,431 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BUDGET IMPORT TEMPLATE — MARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
+          <t>MARY · Budget Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Marquez Project Solutions LLC  ·  appmary.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+          <t>Management And Resources Yield  ·  marquez-project-solutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS:  1. 'Category' column: select Stage, Sub-stage or Activity from the dropdown list.  2. Quantity: number of units.  3. Unit: m, m2, m3, kg, ea, etc.  4. Labor, Materials, Equipment: enter UNIT COST (not total).  5. Unit Price is calculated automatically.  6. Do NOT edit the green column.  7. Save as .xlsx before importing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+          <t>📋  INSTRUCTIONS: Column A = Category (Stage / Sub-stage / Activity)  •  Only "Activity" rows require Unit, Quantity, and costs  •  Do not modify the column headers in row 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Category*</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Description*</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Unit of Measure*</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Quantity*</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Equipment / Transport</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>* Required fields  |  Green column = automatic calculation — do not edit</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Transport / Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Preliminary Works</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="9">
-        <f>IF(OR(D6="—",D6="",D6=0),"",D6*(E6+F6+G6))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Civil Works</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Sub-stage</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Preliminary Works</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr"/>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="9">
-        <f>IF(OR(D7="—",D7="",D7=0),"",D7*(E7+F7+G7))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Earthworks</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Initial Clearing</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="E8" s="15" t="n">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Manual excavation</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>yd³</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Compacted backfill</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>yd³</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Sub-stage</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Concrete Structures</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>3000 PSI concrete columns</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>yd³</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="H8" s="9">
-        <f>IF(OR(D8="—",D8="",D8=0),"",D8*(E8+F8+G8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="F11" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Layout &amp; Leveling</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="9">
-        <f>IF(OR(D9="—",D9="",D9=0),"",D9*(E9+F9+G9))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Steel column reinforcement</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>lb</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="13" t="inlineStr"/>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="9">
-        <f>IF(OR(D10="—",D10="",D10=0),"",D10*(E10+F10+G10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Sub-stage</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr"/>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr"/>
-      <c r="H11" s="9">
-        <f>IF(OR(D11="—",D11="",D11=0),"",D11*(E11+F11+G11))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Finishes</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Manual Excavation</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F12" s="15" t="n">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Wall plastering</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>ft²</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="9">
-        <f>IF(OR(D12="—",D12="",D12=0),"",D12*(E12+F12+G12))</f>
-        <v/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Interior paint (2 coats)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>ft²</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>* Category and Description are required  •  Costs in project currency  •  Technology that understands the build · MPS LLC</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="A6:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Stage,Sub-stage,Activity"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -897,167 +1021,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>UNITS OF MEASURE — REFERENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Valid Category Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Linear meter</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Square meter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Cubic meter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Kilogram</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Metric ton</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Gallon</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>lt</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Liter</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Unit / Each</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>hr</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Hour</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Work day</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>glb</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Global / Lump sum</t>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>Requires costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>Groups sub-stages. No direct costs.</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Sub-stage</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Groups activities within a stage.</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Cost item. Requires Unit, Quantity, and costs.</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
